--- a/output/2025_grupo_etario_por_comuna.xlsx
+++ b/output/2025_grupo_etario_por_comuna.xlsx
@@ -451,16 +451,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -476,7 +468,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -484,30 +476,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,276 +780,276 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:89">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" t="s">
         <v>48</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" t="s">
         <v>49</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" t="s">
         <v>51</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BB1" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" t="s">
         <v>53</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" t="s">
         <v>54</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" t="s">
         <v>55</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BF1" t="s">
         <v>56</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" t="s">
         <v>57</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" t="s">
         <v>58</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" t="s">
         <v>59</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BJ1" t="s">
         <v>60</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" t="s">
         <v>61</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BL1" t="s">
         <v>62</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BM1" t="s">
         <v>63</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" t="s">
         <v>64</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BO1" t="s">
         <v>65</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BP1" t="s">
         <v>66</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BQ1" t="s">
         <v>67</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BR1" t="s">
         <v>68</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BS1" t="s">
         <v>69</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BT1" t="s">
         <v>70</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BU1" t="s">
         <v>71</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BV1" t="s">
         <v>72</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BW1" t="s">
         <v>73</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BX1" t="s">
         <v>74</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BY1" t="s">
         <v>75</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="BZ1" t="s">
         <v>76</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CA1" t="s">
         <v>77</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CB1" t="s">
         <v>78</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CC1" t="s">
         <v>79</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CD1" t="s">
         <v>80</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CE1" t="s">
         <v>81</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CF1" t="s">
         <v>82</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CG1" t="s">
         <v>83</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CH1" t="s">
         <v>84</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CI1" t="s">
         <v>85</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CJ1" t="s">
         <v>86</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CK1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:89">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -1287,11 +1261,11 @@
       </c>
     </row>
     <row r="3" spans="1:89">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
-        <v>3199</v>
+        <v>2983</v>
       </c>
       <c r="C3">
         <v>1272</v>
@@ -1300,7 +1274,7 @@
         <v>2267</v>
       </c>
       <c r="E3">
-        <v>4471</v>
+        <v>4255</v>
       </c>
       <c r="F3">
         <v>357</v>
@@ -1312,7 +1286,7 @@
         <v>3766</v>
       </c>
       <c r="J3">
-        <v>1901</v>
+        <v>1761</v>
       </c>
       <c r="K3">
         <v>748</v>
@@ -1321,7 +1295,7 @@
         <v>1145</v>
       </c>
       <c r="M3">
-        <v>2649</v>
+        <v>2509</v>
       </c>
       <c r="N3">
         <v>78</v>
@@ -1333,7 +1307,7 @@
         <v>1764</v>
       </c>
       <c r="R3">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="S3">
         <v>75</v>
@@ -1342,7 +1316,7 @@
         <v>124</v>
       </c>
       <c r="U3">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="V3">
         <v>5</v>
@@ -1354,7 +1328,7 @@
         <v>148</v>
       </c>
       <c r="Z3">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AA3">
         <v>19</v>
@@ -1363,13 +1337,13 @@
         <v>26</v>
       </c>
       <c r="AC3">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AG3">
         <v>39</v>
       </c>
       <c r="AH3">
-        <v>695</v>
+        <v>648</v>
       </c>
       <c r="AI3">
         <v>254</v>
@@ -1378,7 +1352,7 @@
         <v>470</v>
       </c>
       <c r="AK3">
-        <v>949</v>
+        <v>902</v>
       </c>
       <c r="AL3">
         <v>124</v>
@@ -1390,7 +1364,7 @@
         <v>912</v>
       </c>
       <c r="AP3">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="AQ3">
         <v>171</v>
@@ -1399,7 +1373,7 @@
         <v>494</v>
       </c>
       <c r="AS3">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="AT3">
         <v>150</v>
@@ -1411,19 +1385,19 @@
         <v>903</v>
       </c>
       <c r="AX3">
-        <v>59.4248202563301</v>
+        <v>59.03452899765337</v>
       </c>
       <c r="AY3">
-        <v>6.658330728352611</v>
+        <v>6.738183037210861</v>
       </c>
       <c r="AZ3">
-        <v>1.875586120662707</v>
+        <v>1.944351324170298</v>
       </c>
       <c r="BA3">
-        <v>21.72553923100969</v>
+        <v>21.7230975527992</v>
       </c>
       <c r="BB3">
-        <v>8.471397311659894</v>
+        <v>8.447871270533021</v>
       </c>
       <c r="BC3">
         <v>58.80503144654088</v>
@@ -1456,19 +1430,19 @@
         <v>21.79091310101456</v>
       </c>
       <c r="BM3">
-        <v>59.24849027063297</v>
+        <v>58.96592244418331</v>
       </c>
       <c r="BN3">
-        <v>6.441511966003131</v>
+        <v>6.486486486486487</v>
       </c>
       <c r="BO3">
-        <v>1.766942518452248</v>
+        <v>1.809635722679201</v>
       </c>
       <c r="BP3">
-        <v>21.22567658242004</v>
+        <v>21.19858989424207</v>
       </c>
       <c r="BQ3">
-        <v>9.885931558935361</v>
+        <v>9.941245593419506</v>
       </c>
       <c r="BR3">
         <v>21.84873949579832</v>
@@ -1511,7 +1485,7 @@
       </c>
     </row>
     <row r="4" spans="1:89">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -1527,7 +1501,7 @@
         <v>1260</v>
       </c>
       <c r="F4">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H4">
         <v>1356</v>
@@ -1626,7 +1600,7 @@
         <v>176</v>
       </c>
       <c r="AT4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AV4">
         <v>337</v>
@@ -1695,16 +1669,16 @@
         <v>13.96825396825397</v>
       </c>
       <c r="BR4">
-        <v>21.7948717948718</v>
+        <v>22.07792207792208</v>
       </c>
       <c r="BS4">
-        <v>2.564102564102564</v>
+        <v>2.597402597402597</v>
       </c>
       <c r="BU4">
-        <v>21.7948717948718</v>
+        <v>22.07792207792208</v>
       </c>
       <c r="BV4">
-        <v>53.84615384615385</v>
+        <v>53.24675324675324</v>
       </c>
       <c r="CB4">
         <v>37.38938053097345</v>
@@ -1735,7 +1709,7 @@
       </c>
     </row>
     <row r="5" spans="1:89">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -1959,7 +1933,7 @@
       </c>
     </row>
     <row r="6" spans="1:89">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -2204,7 +2178,7 @@
       </c>
     </row>
     <row r="7" spans="1:89">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -2455,7 +2429,7 @@
       </c>
     </row>
     <row r="8" spans="1:89">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -2706,7 +2680,7 @@
       </c>
     </row>
     <row r="9" spans="1:89">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -2939,7 +2913,7 @@
       </c>
     </row>
     <row r="10" spans="1:89">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -3184,7 +3158,7 @@
       </c>
     </row>
     <row r="11" spans="1:89">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -3408,7 +3382,7 @@
       </c>
     </row>
     <row r="12" spans="1:89">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -3653,7 +3627,7 @@
       </c>
     </row>
     <row r="13" spans="1:89">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -3904,7 +3878,7 @@
       </c>
     </row>
     <row r="14" spans="1:89">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -4149,7 +4123,7 @@
       </c>
     </row>
     <row r="15" spans="1:89">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -4367,7 +4341,7 @@
       </c>
     </row>
     <row r="16" spans="1:89">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -4612,7 +4586,7 @@
       </c>
     </row>
     <row r="17" spans="1:89">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -4857,252 +4831,246 @@
       </c>
     </row>
     <row r="18" spans="1:89">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>3068</v>
+        <v>2473</v>
       </c>
       <c r="C18">
-        <v>1584</v>
+        <v>1248</v>
       </c>
       <c r="D18">
-        <v>3048</v>
+        <v>2438</v>
       </c>
       <c r="E18">
-        <v>4652</v>
+        <v>3721</v>
       </c>
       <c r="F18">
-        <v>512</v>
+        <v>428</v>
       </c>
       <c r="G18">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H18">
-        <v>7257</v>
+        <v>4996</v>
       </c>
       <c r="I18">
-        <v>3292</v>
+        <v>2597</v>
       </c>
       <c r="J18">
-        <v>1878</v>
+        <v>1497</v>
       </c>
       <c r="K18">
-        <v>841</v>
+        <v>633</v>
       </c>
       <c r="L18">
-        <v>1488</v>
+        <v>1142</v>
       </c>
       <c r="M18">
-        <v>2719</v>
+        <v>2130</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="O18">
         <v>2</v>
       </c>
       <c r="P18">
-        <v>2356</v>
+        <v>1589</v>
       </c>
       <c r="Q18">
-        <v>1440</v>
+        <v>1151</v>
       </c>
       <c r="R18">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="S18">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="T18">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="U18">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>678</v>
+        <v>398</v>
       </c>
       <c r="Y18">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="Z18">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AC18">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="AG18">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AH18">
-        <v>699</v>
+        <v>567</v>
       </c>
       <c r="AI18">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="AJ18">
-        <v>614</v>
+        <v>511</v>
       </c>
       <c r="AK18">
-        <v>1050</v>
+        <v>863</v>
       </c>
       <c r="AL18">
-        <v>169</v>
-      </c>
-      <c r="AM18">
+        <v>145</v>
+      </c>
+      <c r="AN18">
+        <v>1520</v>
+      </c>
+      <c r="AO18">
+        <v>585</v>
+      </c>
+      <c r="AP18">
+        <v>283</v>
+      </c>
+      <c r="AQ18">
+        <v>261</v>
+      </c>
+      <c r="AR18">
+        <v>670</v>
+      </c>
+      <c r="AS18">
+        <v>544</v>
+      </c>
+      <c r="AT18">
+        <v>195</v>
+      </c>
+      <c r="AU18">
         <v>2</v>
       </c>
-      <c r="AN18">
-        <v>2175</v>
-      </c>
-      <c r="AO18">
-        <v>749</v>
-      </c>
-      <c r="AP18">
-        <v>333</v>
-      </c>
-      <c r="AQ18">
-        <v>304</v>
-      </c>
-      <c r="AR18">
-        <v>791</v>
-      </c>
-      <c r="AS18">
-        <v>637</v>
-      </c>
-      <c r="AT18">
-        <v>234</v>
-      </c>
-      <c r="AU18">
-        <v>8</v>
-      </c>
       <c r="AV18">
-        <v>2048</v>
+        <v>1489</v>
       </c>
       <c r="AW18">
-        <v>939</v>
+        <v>731</v>
       </c>
       <c r="AX18">
-        <v>61.21251629726206</v>
+        <v>60.53376465830974</v>
       </c>
       <c r="AY18">
-        <v>4.595827900912647</v>
+        <v>4.771532551556813</v>
       </c>
       <c r="AZ18">
-        <v>0.5541069100391134</v>
+        <v>0.3234937323089365</v>
       </c>
       <c r="BA18">
-        <v>22.78357235984355</v>
+        <v>22.92761827739588</v>
       </c>
       <c r="BB18">
-        <v>10.85397653194263</v>
+        <v>11.44359078042863</v>
       </c>
       <c r="BC18">
-        <v>53.09343434343435</v>
+        <v>50.72115384615385</v>
       </c>
       <c r="BD18">
-        <v>4.924242424242424</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="BE18">
-        <v>0.6313131313131313</v>
+        <v>0.5608974358974359</v>
       </c>
       <c r="BF18">
-        <v>22.15909090909091</v>
+        <v>23.71794871794872</v>
       </c>
       <c r="BG18">
-        <v>19.19191919191919</v>
+        <v>20.91346153846154</v>
       </c>
       <c r="BH18">
-        <v>48.81889763779527</v>
+        <v>46.8416735028712</v>
       </c>
       <c r="BI18">
-        <v>4.461942257217848</v>
+        <v>4.142739950779327</v>
       </c>
       <c r="BJ18">
-        <v>0.6233595800524935</v>
+        <v>0.5742411812961444</v>
       </c>
       <c r="BK18">
-        <v>20.14435695538058</v>
+        <v>20.95980311730927</v>
       </c>
       <c r="BL18">
-        <v>25.95144356955381</v>
+        <v>27.48154224774405</v>
       </c>
       <c r="BM18">
-        <v>58.44797936371453</v>
+        <v>57.24267669981188</v>
       </c>
       <c r="BN18">
-        <v>4.707652622527945</v>
+        <v>4.541789841440473</v>
       </c>
       <c r="BO18">
-        <v>0.5803955288048152</v>
+        <v>0.403117441547971</v>
       </c>
       <c r="BP18">
-        <v>22.57093723129837</v>
+        <v>23.19269013705993</v>
       </c>
       <c r="BQ18">
-        <v>13.69303525365434</v>
+        <v>14.61972588013975</v>
       </c>
       <c r="BR18">
-        <v>19.53125</v>
+        <v>18.92523364485981</v>
       </c>
       <c r="BS18">
-        <v>1.7578125</v>
+        <v>1.635514018691589</v>
       </c>
       <c r="BU18">
-        <v>33.0078125</v>
+        <v>33.87850467289719</v>
       </c>
       <c r="BV18">
-        <v>45.703125</v>
+        <v>45.5607476635514</v>
       </c>
       <c r="BW18">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="BZ18">
-        <v>16.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="CA18">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="CB18">
-        <v>32.46520600799229</v>
+        <v>31.80544435548439</v>
       </c>
       <c r="CC18">
-        <v>9.342703596527491</v>
+        <v>7.966373098478783</v>
       </c>
       <c r="CE18">
-        <v>29.97106242248863</v>
+        <v>30.42433947157726</v>
       </c>
       <c r="CF18">
-        <v>28.2210279729916</v>
+        <v>29.80384307445957</v>
       </c>
       <c r="CG18">
-        <v>43.74240583232078</v>
+        <v>44.32036965729688</v>
       </c>
       <c r="CH18">
-        <v>4.434993924665856</v>
+        <v>4.582210242587601</v>
       </c>
       <c r="CI18">
-        <v>0.5467800729040098</v>
+        <v>0.4235656526761648</v>
       </c>
       <c r="CJ18">
-        <v>22.75212636695018</v>
+        <v>22.52599152868695</v>
       </c>
       <c r="CK18">
-        <v>28.52369380315917</v>
+        <v>28.14786291875241</v>
       </c>
     </row>
     <row r="19" spans="1:89">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -5347,7 +5315,7 @@
       </c>
     </row>
     <row r="20" spans="1:89">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -5592,7 +5560,7 @@
       </c>
     </row>
     <row r="21" spans="1:89">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -5608,16 +5576,16 @@
         <v>5528</v>
       </c>
       <c r="F21">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="G21">
         <v>126</v>
       </c>
       <c r="H21">
-        <v>3981</v>
+        <v>4290</v>
       </c>
       <c r="I21">
-        <v>2602</v>
+        <v>2841</v>
       </c>
       <c r="J21">
         <v>2173</v>
@@ -5632,16 +5600,16 @@
         <v>3368</v>
       </c>
       <c r="N21">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="O21">
         <v>29</v>
       </c>
       <c r="P21">
-        <v>1393</v>
+        <v>1499</v>
       </c>
       <c r="Q21">
-        <v>1149</v>
+        <v>1258</v>
       </c>
       <c r="R21">
         <v>262</v>
@@ -5656,16 +5624,16 @@
         <v>375</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>1</v>
       </c>
       <c r="X21">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="Y21">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Z21">
         <v>42</v>
@@ -5680,7 +5648,7 @@
         <v>60</v>
       </c>
       <c r="AG21">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AH21">
         <v>713</v>
@@ -5695,16 +5663,16 @@
         <v>1098</v>
       </c>
       <c r="AL21">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="AM21">
         <v>34</v>
       </c>
       <c r="AN21">
-        <v>1161</v>
+        <v>1250</v>
       </c>
       <c r="AO21">
-        <v>617</v>
+        <v>670</v>
       </c>
       <c r="AP21">
         <v>318</v>
@@ -5719,16 +5687,16 @@
         <v>626</v>
       </c>
       <c r="AT21">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="AU21">
         <v>62</v>
       </c>
       <c r="AV21">
-        <v>1021</v>
+        <v>1099</v>
       </c>
       <c r="AW21">
-        <v>619</v>
+        <v>687</v>
       </c>
       <c r="AX21">
         <v>61.92647477913935</v>
@@ -5791,16 +5759,16 @@
         <v>11.32416787264834</v>
       </c>
       <c r="BR21">
-        <v>27.7027027027027</v>
+        <v>27.75510204081633</v>
       </c>
       <c r="BS21">
-        <v>2.027027027027027</v>
+        <v>2.040816326530612</v>
       </c>
       <c r="BU21">
-        <v>28.82882882882883</v>
+        <v>29.18367346938776</v>
       </c>
       <c r="BV21">
-        <v>41.44144144144144</v>
+        <v>41.02040816326531</v>
       </c>
       <c r="BW21">
         <v>23.01587301587302</v>
@@ -5815,35 +5783,35 @@
         <v>49.20634920634921</v>
       </c>
       <c r="CB21">
-        <v>34.99120823913589</v>
+        <v>34.94172494172494</v>
       </c>
       <c r="CC21">
-        <v>10.19844260236122</v>
+        <v>10.3030303030303</v>
       </c>
       <c r="CE21">
-        <v>29.16352675207234</v>
+        <v>29.13752913752914</v>
       </c>
       <c r="CF21">
-        <v>25.64682240643054</v>
+        <v>25.61771561771562</v>
       </c>
       <c r="CG21">
-        <v>44.15833973866257</v>
+        <v>44.28018303414291</v>
       </c>
       <c r="CH21">
-        <v>6.302843966179862</v>
+        <v>5.843013023583246</v>
       </c>
       <c r="CI21">
-        <v>2.036894696387394</v>
+        <v>2.111932418162619</v>
       </c>
       <c r="CJ21">
-        <v>23.71252882398155</v>
+        <v>23.58324533614924</v>
       </c>
       <c r="CK21">
-        <v>23.78939277478862</v>
+        <v>24.18162618796199</v>
       </c>
     </row>
     <row r="22" spans="1:89">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -6094,7 +6062,7 @@
       </c>
     </row>
     <row r="23" spans="1:89">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -6339,7 +6307,7 @@
       </c>
     </row>
     <row r="24" spans="1:89">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -6361,7 +6329,7 @@
         <v>155</v>
       </c>
       <c r="H24">
-        <v>5294</v>
+        <v>5235</v>
       </c>
       <c r="I24">
         <v>2205</v>
@@ -6385,7 +6353,7 @@
         <v>41</v>
       </c>
       <c r="P24">
-        <v>1779</v>
+        <v>1765</v>
       </c>
       <c r="Q24">
         <v>836</v>
@@ -6409,7 +6377,7 @@
         <v>4</v>
       </c>
       <c r="X24">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Y24">
         <v>110</v>
@@ -6448,7 +6416,7 @@
         <v>43</v>
       </c>
       <c r="AN24">
-        <v>1576</v>
+        <v>1543</v>
       </c>
       <c r="AO24">
         <v>543</v>
@@ -6472,7 +6440,7 @@
         <v>67</v>
       </c>
       <c r="AV24">
-        <v>1397</v>
+        <v>1386</v>
       </c>
       <c r="AW24">
         <v>697</v>
@@ -6562,16 +6530,16 @@
         <v>43.2258064516129</v>
       </c>
       <c r="CB24">
-        <v>33.60408009066868</v>
+        <v>33.71537726838586</v>
       </c>
       <c r="CC24">
-        <v>10.23800528900642</v>
+        <v>10.33428844317096</v>
       </c>
       <c r="CE24">
-        <v>29.7695504344541</v>
+        <v>29.47468958930277</v>
       </c>
       <c r="CF24">
-        <v>26.3883641858708</v>
+        <v>26.4756446991404</v>
       </c>
       <c r="CG24">
         <v>37.91383219954648</v>
@@ -6590,7 +6558,7 @@
       </c>
     </row>
     <row r="25" spans="1:89">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -6841,7 +6809,7 @@
       </c>
     </row>
     <row r="26" spans="1:89">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -7080,7 +7048,7 @@
       </c>
     </row>
     <row r="27" spans="1:89">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -7331,7 +7299,7 @@
       </c>
     </row>
     <row r="28" spans="1:89">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -7543,7 +7511,7 @@
       </c>
     </row>
     <row r="29" spans="1:89">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -7794,7 +7762,7 @@
       </c>
     </row>
     <row r="30" spans="1:89">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -8045,7 +8013,7 @@
       </c>
     </row>
     <row r="31" spans="1:89">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -8284,7 +8252,7 @@
       </c>
     </row>
     <row r="32" spans="1:89">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -8529,7 +8497,7 @@
       </c>
     </row>
     <row r="33" spans="1:89">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -8774,7 +8742,7 @@
       </c>
     </row>
     <row r="34" spans="1:89">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -9025,7 +8993,7 @@
       </c>
     </row>
     <row r="35" spans="1:89">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -9243,7 +9211,7 @@
       </c>
     </row>
     <row r="36" spans="1:89">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -9488,7 +9456,7 @@
       </c>
     </row>
     <row r="37" spans="1:89">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -9733,7 +9701,7 @@
       </c>
     </row>
     <row r="38" spans="1:89">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -9749,10 +9717,10 @@
         <v>10896</v>
       </c>
       <c r="F38">
-        <v>1955</v>
+        <v>1762</v>
       </c>
       <c r="G38">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="H38">
         <v>14114</v>
@@ -9773,10 +9741,10 @@
         <v>7163</v>
       </c>
       <c r="N38">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="O38">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="P38">
         <v>4992</v>
@@ -9797,7 +9765,7 @@
         <v>333</v>
       </c>
       <c r="V38">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="W38">
         <v>1</v>
@@ -9836,7 +9804,7 @@
         <v>2289</v>
       </c>
       <c r="AL38">
-        <v>597</v>
+        <v>544</v>
       </c>
       <c r="AM38">
         <v>11</v>
@@ -9860,10 +9828,10 @@
         <v>1065</v>
       </c>
       <c r="AT38">
-        <v>817</v>
+        <v>719</v>
       </c>
       <c r="AU38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV38">
         <v>3497</v>
@@ -9932,28 +9900,28 @@
         <v>9.774229074889869</v>
       </c>
       <c r="BR38">
-        <v>26.03580562659847</v>
+        <v>26.78774120317821</v>
       </c>
       <c r="BS38">
-        <v>1.636828644501279</v>
+        <v>1.532349602724177</v>
       </c>
       <c r="BU38">
-        <v>30.53708439897698</v>
+        <v>30.87400681044268</v>
       </c>
       <c r="BV38">
-        <v>41.79028132992327</v>
+        <v>40.80590238365494</v>
       </c>
       <c r="BW38">
-        <v>83.72093023255815</v>
+        <v>83.19327731092437</v>
       </c>
       <c r="BX38">
-        <v>0.7751937984496124</v>
+        <v>0.8403361344537815</v>
       </c>
       <c r="BZ38">
-        <v>8.527131782945736</v>
+        <v>9.243697478991596</v>
       </c>
       <c r="CA38">
-        <v>6.976744186046512</v>
+        <v>6.722689075630252</v>
       </c>
       <c r="CB38">
         <v>35.36913702706533</v>
@@ -9984,7 +9952,7 @@
       </c>
     </row>
     <row r="39" spans="1:89">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -10223,7 +10191,7 @@
       </c>
     </row>
     <row r="40" spans="1:89">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -10468,7 +10436,7 @@
       </c>
     </row>
     <row r="41" spans="1:89">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -10719,7 +10687,7 @@
       </c>
     </row>
     <row r="42" spans="1:89">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -10964,7 +10932,7 @@
       </c>
     </row>
     <row r="43" spans="1:89">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -11215,7 +11183,7 @@
       </c>
     </row>
     <row r="44" spans="1:89">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -11466,7 +11434,7 @@
       </c>
     </row>
     <row r="45" spans="1:89">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -11690,7 +11658,7 @@
       </c>
     </row>
     <row r="46" spans="1:89">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -11935,7 +11903,7 @@
       </c>
     </row>
     <row r="47" spans="1:89">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -12153,7 +12121,7 @@
       </c>
     </row>
     <row r="48" spans="1:89">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -12398,7 +12366,7 @@
       </c>
     </row>
     <row r="49" spans="1:89">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -12649,7 +12617,7 @@
       </c>
     </row>
     <row r="50" spans="1:89">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -12867,7 +12835,7 @@
       </c>
     </row>
     <row r="51" spans="1:89">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -13106,7 +13074,7 @@
       </c>
     </row>
     <row r="52" spans="1:89">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -13321,7 +13289,7 @@
       </c>
     </row>
     <row r="53" spans="1:89">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -13555,45 +13523,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -13631,45 +13599,45 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
-        <v>3199</v>
+        <v>2983</v>
       </c>
       <c r="C3">
-        <v>1901</v>
+        <v>1761</v>
       </c>
       <c r="D3">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E3">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F3">
-        <v>695</v>
+        <v>648</v>
       </c>
       <c r="G3">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="H3">
-        <v>59.4248202563301</v>
+        <v>59.03452899765337</v>
       </c>
       <c r="I3">
-        <v>6.658330728352611</v>
+        <v>6.738183037210861</v>
       </c>
       <c r="J3">
-        <v>1.875586120662707</v>
+        <v>1.944351324170298</v>
       </c>
       <c r="K3">
-        <v>21.72553923100969</v>
+        <v>21.7230975527992</v>
       </c>
       <c r="L3">
-        <v>8.471397311659894</v>
+        <v>8.447871270533021</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -13707,7 +13675,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -13745,7 +13713,7 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -13783,7 +13751,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -13821,7 +13789,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -13859,7 +13827,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -13897,7 +13865,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -13935,7 +13903,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -13973,7 +13941,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -14011,7 +13979,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -14049,7 +14017,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -14087,7 +14055,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -14125,7 +14093,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -14163,7 +14131,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -14201,45 +14169,45 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>3068</v>
+        <v>2473</v>
       </c>
       <c r="C18">
-        <v>1878</v>
+        <v>1497</v>
       </c>
       <c r="D18">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>699</v>
+        <v>567</v>
       </c>
       <c r="G18">
-        <v>333</v>
+        <v>283</v>
       </c>
       <c r="H18">
-        <v>61.21251629726206</v>
+        <v>60.53376465830974</v>
       </c>
       <c r="I18">
-        <v>4.595827900912647</v>
+        <v>4.771532551556813</v>
       </c>
       <c r="J18">
-        <v>0.5541069100391134</v>
+        <v>0.3234937323089365</v>
       </c>
       <c r="K18">
-        <v>22.78357235984355</v>
+        <v>22.92761827739588</v>
       </c>
       <c r="L18">
-        <v>10.85397653194263</v>
+        <v>11.44359078042863</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -14277,7 +14245,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -14315,7 +14283,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -14353,7 +14321,7 @@
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -14391,7 +14359,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -14429,7 +14397,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -14467,7 +14435,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -14505,7 +14473,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -14543,7 +14511,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -14581,7 +14549,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -14619,7 +14587,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -14657,7 +14625,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -14695,7 +14663,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -14733,7 +14701,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -14771,7 +14739,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -14809,7 +14777,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -14847,7 +14815,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -14885,7 +14853,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -14923,7 +14891,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -14961,7 +14929,7 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -14999,7 +14967,7 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -15037,7 +15005,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -15075,7 +15043,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -15113,7 +15081,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -15151,7 +15119,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -15189,7 +15157,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -15227,7 +15195,7 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -15265,7 +15233,7 @@
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -15303,7 +15271,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -15341,7 +15309,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -15379,7 +15347,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -15417,7 +15385,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -15455,7 +15423,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -15493,7 +15461,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -15525,7 +15493,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -15573,45 +15541,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>54</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -15649,7 +15617,7 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -15687,7 +15655,7 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -15725,7 +15693,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -15763,7 +15731,7 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -15801,7 +15769,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -15839,7 +15807,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -15877,7 +15845,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -15915,7 +15883,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -15953,7 +15921,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -15991,7 +15959,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -16029,7 +15997,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -16067,7 +16035,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -16105,7 +16073,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -16143,7 +16111,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -16181,7 +16149,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -16219,45 +16187,45 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>1584</v>
+        <v>1248</v>
       </c>
       <c r="C18">
-        <v>841</v>
+        <v>633</v>
       </c>
       <c r="D18">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="E18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F18">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="G18">
-        <v>304</v>
+        <v>261</v>
       </c>
       <c r="H18">
-        <v>53.09343434343435</v>
+        <v>50.72115384615385</v>
       </c>
       <c r="I18">
-        <v>4.924242424242424</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="J18">
-        <v>0.6313131313131313</v>
+        <v>0.5608974358974359</v>
       </c>
       <c r="K18">
-        <v>22.15909090909091</v>
+        <v>23.71794871794872</v>
       </c>
       <c r="L18">
-        <v>19.19191919191919</v>
+        <v>20.91346153846154</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -16295,7 +16263,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -16333,7 +16301,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -16371,7 +16339,7 @@
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -16409,7 +16377,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -16447,7 +16415,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -16485,7 +16453,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -16523,7 +16491,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -16561,7 +16529,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -16599,7 +16567,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -16637,7 +16605,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -16675,7 +16643,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -16713,7 +16681,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -16751,7 +16719,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -16789,7 +16757,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -16827,7 +16795,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -16865,7 +16833,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -16903,7 +16871,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -16941,7 +16909,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -16979,7 +16947,7 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -17017,7 +16985,7 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -17055,7 +17023,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -17093,7 +17061,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -17131,7 +17099,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -17169,7 +17137,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -17207,7 +17175,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -17245,7 +17213,7 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -17283,7 +17251,7 @@
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -17321,7 +17289,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -17359,7 +17327,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -17397,7 +17365,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -17435,7 +17403,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -17473,7 +17441,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -17511,7 +17479,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -17543,7 +17511,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -17591,45 +17559,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>59</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>60</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>61</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -17667,7 +17635,7 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -17705,7 +17673,7 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -17743,7 +17711,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -17781,7 +17749,7 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -17819,7 +17787,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -17857,7 +17825,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -17895,7 +17863,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -17933,7 +17901,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -17971,7 +17939,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -18009,7 +17977,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -18047,7 +18015,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -18085,7 +18053,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -18123,7 +18091,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -18161,7 +18129,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -18199,7 +18167,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -18237,45 +18205,45 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>3048</v>
+        <v>2438</v>
       </c>
       <c r="C18">
-        <v>1488</v>
+        <v>1142</v>
       </c>
       <c r="D18">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="E18">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F18">
-        <v>614</v>
+        <v>511</v>
       </c>
       <c r="G18">
-        <v>791</v>
+        <v>670</v>
       </c>
       <c r="H18">
-        <v>48.81889763779527</v>
+        <v>46.8416735028712</v>
       </c>
       <c r="I18">
-        <v>4.461942257217848</v>
+        <v>4.142739950779327</v>
       </c>
       <c r="J18">
-        <v>0.6233595800524935</v>
+        <v>0.5742411812961444</v>
       </c>
       <c r="K18">
-        <v>20.14435695538058</v>
+        <v>20.95980311730927</v>
       </c>
       <c r="L18">
-        <v>25.95144356955381</v>
+        <v>27.48154224774405</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -18313,7 +18281,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -18351,7 +18319,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -18389,7 +18357,7 @@
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -18427,7 +18395,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -18465,7 +18433,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -18503,7 +18471,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -18541,7 +18509,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -18579,7 +18547,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -18617,7 +18585,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -18655,7 +18623,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -18693,7 +18661,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -18731,7 +18699,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -18769,7 +18737,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -18807,7 +18775,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -18845,7 +18813,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -18883,7 +18851,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -18921,7 +18889,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -18959,7 +18927,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -18997,7 +18965,7 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -19035,7 +19003,7 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -19073,7 +19041,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -19111,7 +19079,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -19149,7 +19117,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -19187,7 +19155,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -19225,7 +19193,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -19263,7 +19231,7 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -19301,7 +19269,7 @@
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -19339,7 +19307,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -19377,7 +19345,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -19415,7 +19383,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -19453,7 +19421,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -19491,7 +19459,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -19523,7 +19491,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -19555,7 +19523,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -19603,45 +19571,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -19679,45 +19647,45 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
-        <v>4471</v>
+        <v>4255</v>
       </c>
       <c r="C3">
-        <v>2649</v>
+        <v>2509</v>
       </c>
       <c r="D3">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E3">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F3">
-        <v>949</v>
+        <v>902</v>
       </c>
       <c r="G3">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="H3">
-        <v>59.24849027063297</v>
+        <v>58.96592244418331</v>
       </c>
       <c r="I3">
-        <v>6.441511966003131</v>
+        <v>6.486486486486487</v>
       </c>
       <c r="J3">
-        <v>1.766942518452248</v>
+        <v>1.809635722679201</v>
       </c>
       <c r="K3">
-        <v>21.22567658242004</v>
+        <v>21.19858989424207</v>
       </c>
       <c r="L3">
-        <v>9.885931558935361</v>
+        <v>9.941245593419506</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -19755,7 +19723,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -19793,7 +19761,7 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -19831,7 +19799,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -19869,7 +19837,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -19907,7 +19875,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -19945,7 +19913,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -19983,7 +19951,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -20021,7 +19989,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -20059,7 +20027,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -20097,7 +20065,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -20135,7 +20103,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -20173,7 +20141,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -20211,7 +20179,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -20249,45 +20217,45 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>4652</v>
+        <v>3721</v>
       </c>
       <c r="C18">
-        <v>2719</v>
+        <v>2130</v>
       </c>
       <c r="D18">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="E18">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F18">
-        <v>1050</v>
+        <v>863</v>
       </c>
       <c r="G18">
-        <v>637</v>
+        <v>544</v>
       </c>
       <c r="H18">
-        <v>58.44797936371453</v>
+        <v>57.24267669981188</v>
       </c>
       <c r="I18">
-        <v>4.707652622527945</v>
+        <v>4.541789841440473</v>
       </c>
       <c r="J18">
-        <v>0.5803955288048152</v>
+        <v>0.403117441547971</v>
       </c>
       <c r="K18">
-        <v>22.57093723129837</v>
+        <v>23.19269013705993</v>
       </c>
       <c r="L18">
-        <v>13.69303525365434</v>
+        <v>14.61972588013975</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -20325,7 +20293,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -20363,7 +20331,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -20401,7 +20369,7 @@
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -20439,7 +20407,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -20477,7 +20445,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -20515,7 +20483,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -20553,7 +20521,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -20591,7 +20559,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -20629,7 +20597,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -20667,7 +20635,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -20705,7 +20673,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -20743,7 +20711,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -20781,7 +20749,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -20819,7 +20787,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -20857,7 +20825,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -20895,7 +20863,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -20933,7 +20901,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -20971,7 +20939,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -21009,7 +20977,7 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -21047,7 +21015,7 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -21085,7 +21053,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -21123,7 +21091,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -21161,7 +21129,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -21199,7 +21167,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -21237,7 +21205,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -21275,7 +21243,7 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -21313,7 +21281,7 @@
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -21351,7 +21319,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -21389,7 +21357,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -21427,7 +21395,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -21465,7 +21433,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -21503,7 +21471,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -21541,7 +21509,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -21573,7 +21541,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -21621,45 +21589,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>71</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -21685,7 +21653,7 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -21717,11 +21685,11 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4">
         <v>17</v>
@@ -21733,23 +21701,23 @@
         <v>17</v>
       </c>
       <c r="G4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H4">
-        <v>21.7948717948718</v>
+        <v>22.07792207792208</v>
       </c>
       <c r="I4">
-        <v>2.564102564102564</v>
+        <v>2.597402597402597</v>
       </c>
       <c r="K4">
-        <v>21.7948717948718</v>
+        <v>22.07792207792208</v>
       </c>
       <c r="L4">
-        <v>53.84615384615385</v>
+        <v>53.24675324675324</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -21781,7 +21749,7 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -21813,7 +21781,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -21845,7 +21813,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -21877,7 +21845,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -21909,7 +21877,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -21941,7 +21909,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -21973,7 +21941,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -22005,7 +21973,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -22037,7 +22005,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -22069,7 +22037,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -22095,7 +22063,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -22121,7 +22089,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -22153,39 +22121,39 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>512</v>
+        <v>428</v>
       </c>
       <c r="C18">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="G18">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="H18">
-        <v>19.53125</v>
+        <v>18.92523364485981</v>
       </c>
       <c r="I18">
-        <v>1.7578125</v>
+        <v>1.635514018691589</v>
       </c>
       <c r="K18">
-        <v>33.0078125</v>
+        <v>33.87850467289719</v>
       </c>
       <c r="L18">
-        <v>45.703125</v>
+        <v>45.5607476635514</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -22217,7 +22185,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -22249,39 +22217,39 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="C21">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="G21">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="H21">
-        <v>27.7027027027027</v>
+        <v>27.75510204081633</v>
       </c>
       <c r="I21">
-        <v>2.027027027027027</v>
+        <v>2.040816326530612</v>
       </c>
       <c r="K21">
-        <v>28.82882882882883</v>
+        <v>29.18367346938776</v>
       </c>
       <c r="L21">
-        <v>41.44144144144144</v>
+        <v>41.02040816326531</v>
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -22313,7 +22281,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -22345,7 +22313,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -22377,7 +22345,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -22409,7 +22377,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -22435,7 +22403,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -22467,7 +22435,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -22493,7 +22461,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -22525,7 +22493,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -22557,7 +22525,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -22589,7 +22557,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -22621,7 +22589,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -22653,7 +22621,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -22685,7 +22653,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -22711,7 +22679,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -22743,7 +22711,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -22775,39 +22743,39 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
-        <v>1955</v>
+        <v>1762</v>
       </c>
       <c r="C38">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="D38">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F38">
-        <v>597</v>
+        <v>544</v>
       </c>
       <c r="G38">
-        <v>817</v>
+        <v>719</v>
       </c>
       <c r="H38">
-        <v>26.03580562659847</v>
+        <v>26.78774120317821</v>
       </c>
       <c r="I38">
-        <v>1.636828644501279</v>
+        <v>1.532349602724177</v>
       </c>
       <c r="K38">
-        <v>30.53708439897698</v>
+        <v>30.87400681044268</v>
       </c>
       <c r="L38">
-        <v>41.79028132992327</v>
+        <v>40.80590238365494</v>
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -22839,7 +22807,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -22871,7 +22839,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -22903,7 +22871,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -22935,7 +22903,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -22967,7 +22935,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -22999,7 +22967,7 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -23031,7 +22999,7 @@
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -23063,7 +23031,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -23089,7 +23057,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -23121,7 +23089,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -23153,7 +23121,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -23185,7 +23153,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -23217,7 +23185,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -23243,7 +23211,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -23285,65 +23253,65 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>74</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>75</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>76</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -23369,7 +23337,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -23401,7 +23369,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -23433,7 +23401,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -23447,7 +23415,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -23473,12 +23441,12 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -23504,7 +23472,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -23536,7 +23504,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -23562,12 +23530,12 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -23599,7 +23567,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -23625,33 +23593,27 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>2</v>
       </c>
-      <c r="G18">
-        <v>8</v>
-      </c>
       <c r="H18">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="K18">
-        <v>16.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="L18">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -23677,7 +23639,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -23703,7 +23665,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -23735,7 +23697,7 @@
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -23767,7 +23729,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -23793,7 +23755,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -23825,7 +23787,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -23857,7 +23819,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -23883,7 +23845,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -23915,12 +23877,12 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -23952,7 +23914,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -23984,7 +23946,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -24004,7 +23966,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -24030,7 +23992,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -24056,7 +24018,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -24088,12 +24050,12 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -24119,7 +24081,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -24145,14 +24107,14 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C38">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -24161,23 +24123,23 @@
         <v>11</v>
       </c>
       <c r="G38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H38">
-        <v>83.72093023255815</v>
+        <v>83.19327731092437</v>
       </c>
       <c r="I38">
-        <v>0.7751937984496124</v>
+        <v>0.8403361344537815</v>
       </c>
       <c r="K38">
-        <v>8.527131782945736</v>
+        <v>9.243697478991596</v>
       </c>
       <c r="L38">
-        <v>6.976744186046512</v>
+        <v>6.722689075630252</v>
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -24197,7 +24159,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -24223,7 +24185,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -24255,7 +24217,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -24281,7 +24243,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -24313,7 +24275,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -24345,12 +24307,12 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -24376,12 +24338,12 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -24407,7 +24369,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -24439,12 +24401,12 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -24470,7 +24432,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -24502,7 +24464,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
     </row>
@@ -24517,45 +24479,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>79</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>80</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>81</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -24587,7 +24549,7 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -24619,7 +24581,7 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -24651,7 +24613,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -24683,7 +24645,7 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -24715,7 +24677,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -24747,7 +24709,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -24779,7 +24741,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -24811,7 +24773,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -24843,7 +24805,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -24875,7 +24837,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -24907,7 +24869,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -24939,7 +24901,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -24971,7 +24933,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -25003,7 +24965,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -25035,7 +24997,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -25067,39 +25029,39 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>7257</v>
+        <v>4996</v>
       </c>
       <c r="C18">
-        <v>2356</v>
+        <v>1589</v>
       </c>
       <c r="D18">
-        <v>678</v>
+        <v>398</v>
       </c>
       <c r="F18">
-        <v>2175</v>
+        <v>1520</v>
       </c>
       <c r="G18">
-        <v>2048</v>
+        <v>1489</v>
       </c>
       <c r="H18">
-        <v>32.46520600799229</v>
+        <v>31.80544435548439</v>
       </c>
       <c r="I18">
-        <v>9.342703596527491</v>
+        <v>7.966373098478783</v>
       </c>
       <c r="K18">
-        <v>29.97106242248863</v>
+        <v>30.42433947157726</v>
       </c>
       <c r="L18">
-        <v>28.2210279729916</v>
+        <v>29.80384307445957</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -25131,7 +25093,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -25163,39 +25125,39 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
-        <v>3981</v>
+        <v>4290</v>
       </c>
       <c r="C21">
-        <v>1393</v>
+        <v>1499</v>
       </c>
       <c r="D21">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="F21">
-        <v>1161</v>
+        <v>1250</v>
       </c>
       <c r="G21">
-        <v>1021</v>
+        <v>1099</v>
       </c>
       <c r="H21">
-        <v>34.99120823913589</v>
+        <v>34.94172494172494</v>
       </c>
       <c r="I21">
-        <v>10.19844260236122</v>
+        <v>10.3030303030303</v>
       </c>
       <c r="K21">
-        <v>29.16352675207234</v>
+        <v>29.13752913752914</v>
       </c>
       <c r="L21">
-        <v>25.64682240643054</v>
+        <v>25.61771561771562</v>
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -25227,7 +25189,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -25259,39 +25221,39 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
-        <v>5294</v>
+        <v>5235</v>
       </c>
       <c r="C24">
-        <v>1779</v>
+        <v>1765</v>
       </c>
       <c r="D24">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F24">
-        <v>1576</v>
+        <v>1543</v>
       </c>
       <c r="G24">
-        <v>1397</v>
+        <v>1386</v>
       </c>
       <c r="H24">
-        <v>33.60408009066868</v>
+        <v>33.71537726838586</v>
       </c>
       <c r="I24">
-        <v>10.23800528900642</v>
+        <v>10.33428844317096</v>
       </c>
       <c r="K24">
-        <v>29.7695504344541</v>
+        <v>29.47468958930277</v>
       </c>
       <c r="L24">
-        <v>26.3883641858708</v>
+        <v>26.4756446991404</v>
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -25323,7 +25285,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -25355,7 +25317,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -25387,7 +25349,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -25419,7 +25381,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -25451,7 +25413,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -25483,7 +25445,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -25515,7 +25477,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -25547,7 +25509,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -25579,7 +25541,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -25611,7 +25573,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -25643,7 +25605,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -25675,7 +25637,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -25707,7 +25669,7 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -25739,7 +25701,7 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -25771,7 +25733,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -25803,7 +25765,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -25835,7 +25797,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -25867,7 +25829,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -25899,7 +25861,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -25931,7 +25893,7 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -25963,7 +25925,7 @@
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -25995,7 +25957,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -26027,7 +25989,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -26059,7 +26021,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -26091,7 +26053,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -26123,7 +26085,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -26155,7 +26117,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -26187,7 +26149,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -26229,45 +26191,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>83</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>86</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -26299,7 +26261,7 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -26337,7 +26299,7 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -26375,7 +26337,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -26413,7 +26375,7 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -26451,7 +26413,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -26489,7 +26451,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -26527,7 +26489,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -26565,7 +26527,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -26603,7 +26565,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -26641,7 +26603,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -26679,7 +26641,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -26717,7 +26679,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -26755,7 +26717,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -26793,7 +26755,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -26831,7 +26793,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -26869,45 +26831,45 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
-        <v>3292</v>
+        <v>2597</v>
       </c>
       <c r="C18">
-        <v>1440</v>
+        <v>1151</v>
       </c>
       <c r="D18">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F18">
-        <v>749</v>
+        <v>585</v>
       </c>
       <c r="G18">
-        <v>939</v>
+        <v>731</v>
       </c>
       <c r="H18">
-        <v>43.74240583232078</v>
+        <v>44.32036965729688</v>
       </c>
       <c r="I18">
-        <v>4.434993924665856</v>
+        <v>4.582210242587601</v>
       </c>
       <c r="J18">
-        <v>0.5467800729040098</v>
+        <v>0.4235656526761648</v>
       </c>
       <c r="K18">
-        <v>22.75212636695018</v>
+        <v>22.52599152868695</v>
       </c>
       <c r="L18">
-        <v>28.52369380315917</v>
+        <v>28.14786291875241</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -26945,7 +26907,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -26983,45 +26945,45 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
-        <v>2602</v>
+        <v>2841</v>
       </c>
       <c r="C21">
-        <v>1149</v>
+        <v>1258</v>
       </c>
       <c r="D21">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E21">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F21">
-        <v>617</v>
+        <v>670</v>
       </c>
       <c r="G21">
-        <v>619</v>
+        <v>687</v>
       </c>
       <c r="H21">
-        <v>44.15833973866257</v>
+        <v>44.28018303414291</v>
       </c>
       <c r="I21">
-        <v>6.302843966179862</v>
+        <v>5.843013023583246</v>
       </c>
       <c r="J21">
-        <v>2.036894696387394</v>
+        <v>2.111932418162619</v>
       </c>
       <c r="K21">
-        <v>23.71252882398155</v>
+        <v>23.58324533614924</v>
       </c>
       <c r="L21">
-        <v>23.78939277478862</v>
+        <v>24.18162618796199</v>
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -27059,7 +27021,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -27097,7 +27059,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -27135,7 +27097,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -27173,7 +27135,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -27211,7 +27173,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -27249,7 +27211,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -27281,7 +27243,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -27319,7 +27281,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -27357,7 +27319,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -27395,7 +27357,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -27433,7 +27395,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -27471,7 +27433,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -27509,7 +27471,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -27547,7 +27509,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -27585,7 +27547,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -27623,7 +27585,7 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -27661,7 +27623,7 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -27699,7 +27661,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -27737,7 +27699,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -27775,7 +27737,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -27813,7 +27775,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -27851,7 +27813,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -27889,7 +27851,7 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -27927,7 +27889,7 @@
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -27965,7 +27927,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -28003,7 +27965,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -28041,7 +28003,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -28079,7 +28041,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -28111,7 +28073,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -28149,7 +28111,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -28181,7 +28143,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
